--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -716,6 +716,26 @@
         <v>1359</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>429</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -736,6 +736,16 @@
         <v>429</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>389</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,6 +436,36 @@
       </c>
       <c r="B2" t="n">
         <v>439</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A1FPro</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DYU UX</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>899</v>
       </c>
     </row>
   </sheetData>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -1,34 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\shaham\projects\exc-site\products\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A987A0-6A4E-47C9-B809-E9C68550F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="3510" yWindow="450" windowWidth="38400" windowHeight="21150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>D3S</t>
+  </si>
+  <si>
+    <t>A1FPro</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>DYU UX</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>Purchase Price</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -43,84 +91,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{BA337076-25CC-4A1C-88DD-4998E41A4174}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,64 +404,101 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>D3S</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>380</v>
+      </c>
+      <c r="C2">
         <v>439</v>
       </c>
+      <c r="D2" s="1">
+        <f>(C2-B2)/C2</f>
+        <v>0.13439635535307518</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A1FPro</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>325</v>
+      </c>
+      <c r="C3">
         <v>589</v>
       </c>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D6" si="0">(C3-B3)/C3</f>
+        <v>0.44821731748726656</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>534</v>
+      </c>
+      <c r="C4">
         <v>859</v>
       </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.37834691501746215</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DYU UX</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>590</v>
+      </c>
+      <c r="C5">
         <v>899</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.34371523915461621</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>684</v>
+      </c>
+      <c r="C6">
+        <v>949</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.27924130663856689</v>
       </c>
     </row>
   </sheetData>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -1,82 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\shaham\projects\exc-site\products\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A987A0-6A4E-47C9-B809-E9C68550F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="450" windowWidth="38400" windowHeight="21150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3900" yWindow="450" windowWidth="38400" windowHeight="21150" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>D3S</t>
-  </si>
-  <si>
-    <t>A1FPro</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>DYU UX</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>Purchase Price</t>
-  </si>
-  <si>
-    <t>Profit</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -91,32 +47,88 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{BA337076-25CC-4A1C-88DD-4998E41A4174}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -404,101 +416,84 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>380</v>
-      </c>
-      <c r="C2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D3S</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>439</v>
       </c>
-      <c r="D2" s="1">
-        <f>(C2-B2)/C2</f>
-        <v>0.13439635535307518</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>325</v>
-      </c>
-      <c r="C3">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A1FPro</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>589</v>
       </c>
-      <c r="D3" s="1">
-        <f t="shared" ref="D3:D6" si="0">(C3-B3)/C3</f>
-        <v>0.44821731748726656</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>534</v>
-      </c>
-      <c r="C4">
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>859</v>
       </c>
-      <c r="D4" s="1">
-        <f t="shared" si="0"/>
-        <v>0.37834691501746215</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>590</v>
-      </c>
-      <c r="C5">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DYU UX</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>899</v>
       </c>
-      <c r="D5" s="1">
-        <f t="shared" si="0"/>
-        <v>0.34371523915461621</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>684</v>
-      </c>
-      <c r="C6">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>949</v>
       </c>
-      <c r="D6" s="1">
-        <f t="shared" si="0"/>
-        <v>0.27924130663856689</v>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>509</v>
       </c>
     </row>
   </sheetData>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,16 @@
         <v>509</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SP1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,16 @@
         <v>999</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DYU M20</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>899</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,6 +516,16 @@
         <v>899</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>699</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,6 +526,16 @@
         <v>699</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CampX</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,6 +536,16 @@
         <v>999</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ZX3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1699</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,6 +546,16 @@
         <v>1699</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OT16-2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>729</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,6 +556,16 @@
         <v>729</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OT02</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>499</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,16 @@
         <v>499</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OT02Pro</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>599</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,6 +576,16 @@
         <v>599</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OT05</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1049</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,6 +586,16 @@
         <v>1049</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OT05Pro</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1179</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,6 +596,16 @@
         <v>1179</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OT12</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>749</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,6 +606,16 @@
         <v>749</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C29Lite</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>749</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,6 +616,16 @@
         <v>749</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WT05</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>899</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
